--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
     <sheet name="20260215" sheetId="74" r:id="rId2"/>
     <sheet name="20260222" sheetId="75" r:id="rId3"/>
+    <sheet name="20260308)" sheetId="76" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="112">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -311,6 +312,60 @@
   </si>
   <si>
     <t>A: Wǒ zhēn xǐ huan zhè xiē cōng ming de jī qì rén。</t>
+  </si>
+  <si>
+    <t>A:今天天气好热，我想买点水果解解渴</t>
+  </si>
+  <si>
+    <t>A: It's so hot today. I want to buy some fruits to quench my thirst.</t>
+  </si>
+  <si>
+    <t>Jīn tiān tiān qì hǎo rè, wǒ xiǎng mǎi diǎn shuǐ guǒ jiě jiě kě</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b:太巧了，我也正打算去水果店呢，一起吧？ </t>
+  </si>
+  <si>
+    <t>B: What a coincidence! I was just going to the fruit store too. Shall we go together?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tài qiǎo le, wǒ yě zhèng dǎ suàn qù shuǐ guǒ diàn ne, yī qǐ ba?</t>
+  </si>
+  <si>
+    <t>A:好呀好呀，你平时最喜欢吃什么水果？</t>
+  </si>
+  <si>
+    <t>A: Great! What's your favorite fruit usually?</t>
+  </si>
+  <si>
+    <t>Hǎo ya hǎo ya, nǐ píng shí zuì xǐ huan chī shén me shuǐ guǒ?</t>
+  </si>
+  <si>
+    <t>B:我最喜欢吃草莓，又甜又新鲜，你呢？</t>
+  </si>
+  <si>
+    <t>B: My favorite fruit is strawberry. It's sweet and fresh. What about you?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wǒ zuì xǐ huan chī cǎo méi, yòu tián yòu xīn xiān, nǐ ne? | </t>
+  </si>
+  <si>
+    <t>A: 我偏爱橙子，富含维生素C，还能补充水分</t>
+  </si>
+  <si>
+    <t>A: I prefer oranges. They are rich in vitamin C and can replenish water.</t>
+  </si>
+  <si>
+    <t>Wǒ piān ài chéng zi, fù hán wéi shēng sù C, hái néng bǔ chōng shuǐ fèn.</t>
+  </si>
+  <si>
+    <t>B那太好了，我们去买一点草莓和橙子</t>
+  </si>
+  <si>
+    <t>B: That's great! Let's buy some strawberries and oranges</t>
+  </si>
+  <si>
+    <t>Nà tài hǎo le, wǒ men qù mǎi yī diǎn cǎo méi hé chéng zi</t>
   </si>
 </sst>
 </file>
@@ -2092,4 +2147,124 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:AC23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:23">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:23">
+      <c r="B3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="2:23">
+      <c r="B4" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23">
+      <c r="B6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="W6" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23">
+      <c r="B7" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23">
+      <c r="B10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="W10" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="2:23">
+      <c r="B11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="2:23">
+      <c r="V12" s="3"/>
+    </row>
+    <row r="13" spans="2:23">
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="2:23">
+      <c r="B14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="W14" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="2:23">
+      <c r="B15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="2:23">
+      <c r="C16" s="5"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="18" spans="2:29">
+      <c r="B18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="W18" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29">
+      <c r="B19" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29">
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29">
+      <c r="B22" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29">
+      <c r="AC23" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,13 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
     <sheet name="20260215" sheetId="74" r:id="rId2"/>
     <sheet name="20260222" sheetId="75" r:id="rId3"/>
-    <sheet name="20260308)" sheetId="76" r:id="rId4"/>
+    <sheet name="20260308" sheetId="76" r:id="rId4"/>
+    <sheet name="20260315" sheetId="77" r:id="rId5"/>
+    <sheet name="20260322" sheetId="78" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="162">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -366,6 +368,156 @@
   </si>
   <si>
     <t>Nà tài hǎo le, wǒ men qù mǎi yī diǎn cǎo méi hé chéng zi</t>
+  </si>
+  <si>
+    <t>A:奶奶，你看！那黄色的小花是什么呀？</t>
+  </si>
+  <si>
+    <t>Grandma, look! What are those yellow little flowers?</t>
+  </si>
+  <si>
+    <t>nǎinai, nǐ kàn! Nà huángsè de xiǎohuā shì shénme ya?</t>
+  </si>
+  <si>
+    <t>B:傻孩子，这是迎春花呀，最先来告诉我们春天到啦。</t>
+  </si>
+  <si>
+    <t>Silly child, these are winter jasmine flowers. coming first to tell us that spring has arrived.</t>
+  </si>
+  <si>
+    <t>Shǎ háizi, zhè shì yíngchūnhuā ya, zuìxiān lái gàosu wǒmen chūntiān dào la.</t>
+  </si>
+  <si>
+    <t>A:哇，好香呀！那春天还有什么会来呢？</t>
+  </si>
+  <si>
+    <t>Wā, hǎo xiāng ya! Nà chūntiān hái yǒu shénme huì lái ne?</t>
+  </si>
+  <si>
+    <t>Wow, so fragrant! What else will come in spring?</t>
+  </si>
+  <si>
+    <t>B: 你看那边的柳树，枝条已经变软了，过几天就会冒出嫩绿的小芽</t>
+  </si>
+  <si>
+    <t>Nǐ kàn nàbiān de liǔshù, zhītiáo yǐjīng biàn ruǎn le, guò jǐ tiān jiù huì màochū nènlǜ de xiǎoyá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the willow trees over there. Their branches have become soft. In a few days, </t>
+  </si>
+  <si>
+    <t>A: 太可爱啦！那小鸟会回来吗？我好久没听到小鸟唱歌了。</t>
+  </si>
+  <si>
+    <t>tender green buds will come out</t>
+  </si>
+  <si>
+    <t>Tài kě'ài la! Nà xiǎoniǎo huì huílái ma? Wǒ hǎojiǔ méi tīngdào xiǎoniǎo chànggē le</t>
+  </si>
+  <si>
+    <t>So cute! Will the birds come back? I haven't heard the birds sing for a long time.</t>
+  </si>
+  <si>
+    <t>B: 当然会啦！春天一到，小鸟就会从温暖的地方飞回来，在树上唱歌</t>
+  </si>
+  <si>
+    <t>Dāngrán huì la! Chūntiān yī dào, xiǎoniǎo jiù huì cóng wēnnuǎn de dìfang fēi huílái, zài shù shàng chànggē</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Of course they will! As soon as spring arrives, the birds will fly back from warm places, </t>
+  </si>
+  <si>
+    <t>A:那春天会下雨吗？ 想看到彩虹！</t>
+  </si>
+  <si>
+    <t>sing and build nests on the trees</t>
+  </si>
+  <si>
+    <t>Nà chūntiān huì xià yǔ ma?xiǎng kàndào cǎihóng!</t>
+  </si>
+  <si>
+    <t>Will it rain in spring? I want to see a rainbow!</t>
+  </si>
+  <si>
+    <t>B: 会的呀，说不定真的会有彩虹呢。</t>
+  </si>
+  <si>
+    <t>Yes, it will.  maybe there will really be a rainbow</t>
+  </si>
+  <si>
+    <t>Huì de ya，shuōbudìng zhēn de huì yǒu cǎihóng ne</t>
+  </si>
+  <si>
+    <t>A：嘿，你觉得新AI助手好用吗？它能帮我安排日程。</t>
+  </si>
+  <si>
+    <t>A: Hey, do you think the new AI assistant is useful? It helps me schedule my day.</t>
+  </si>
+  <si>
+    <t>A: Hēi, nǐ juédé xīn AI zhùshǒu hǎoyòng ma? Tā néng bāng wǒ ānpái rìchéng.</t>
+  </si>
+  <si>
+    <t>B：当然！它像人一样思考，还节省时间。</t>
+  </si>
+  <si>
+    <t>B: Definitely! It thinks like a human and saves time.</t>
+  </si>
+  <si>
+    <t>B: Dāngrán! Tā xiàng rén yīyàng sīkǎo, hái jiéshěng shíjiān.</t>
+  </si>
+  <si>
+    <t>A：但AI不是人的智能，只是模拟我们。</t>
+  </si>
+  <si>
+    <t>A: But AI isn't human intelligence; it just simulates us.</t>
+  </si>
+  <si>
+    <t>A: Dàn AI bùshì rén de zhìnéng, zhǐshì mónǐ wǒmen.</t>
+  </si>
+  <si>
+    <t>B：对，但它能解决大问题.</t>
+  </si>
+  <si>
+    <t>B: Right, but it can solve big problems</t>
+  </si>
+  <si>
+    <t>B: Duì, dàn tā néng jiějué dà wèntí</t>
+  </si>
+  <si>
+    <t>A：AI可以优化资源，减少浪费。</t>
+  </si>
+  <si>
+    <t>A: AI can optimize resources and reduce waste.</t>
+  </si>
+  <si>
+    <t>A: AI kěyǐ yōuhuà zīyuán, jiǎnshǎo làngfèi.</t>
+  </si>
+  <si>
+    <t>B：希望未来它能超过人的智能。</t>
+  </si>
+  <si>
+    <t>B: I hope it might surpass human intelligence in the future.</t>
+  </si>
+  <si>
+    <t>B: Xīwàng wèilái tā néng chāoguò rén de zhìnéng.</t>
+  </si>
+  <si>
+    <t>A：我们得拥抱技术，别依赖太多。</t>
+  </si>
+  <si>
+    <t>A: We should embrace technology, but not rely on it too much.</t>
+  </si>
+  <si>
+    <t>A: Wǒmen déi yōngbào jìshù, bié yīlài tài duō.</t>
+  </si>
+  <si>
+    <t>B：同意！AI让生活更高效。</t>
+  </si>
+  <si>
+    <t>B: Agreed! AI makes life more efficient.</t>
+  </si>
+  <si>
+    <t>B: Tóngyì! AI ràng shēnghuó gèng gāoxiào.</t>
   </si>
 </sst>
 </file>
@@ -397,12 +549,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFCE181E"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF1C1C1C"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -412,6 +558,12 @@
       <color rgb="FF1C1C1C"/>
       <name val="等线"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCE181E"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1705,10 +1857,10 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="3"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
@@ -1731,16 +1883,16 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="3"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="3"/>
+      <c r="V22" s="5"/>
     </row>
     <row r="23" spans="2:26">
       <c r="B23" s="2"/>
@@ -1794,7 +1946,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="3"/>
+      <c r="AC33" s="5"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -1895,10 +2047,10 @@
       <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="3"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
@@ -1921,16 +2073,16 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="3"/>
       <c r="U21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="3"/>
+      <c r="V22" s="5"/>
     </row>
     <row r="23" spans="2:26">
       <c r="B23" s="2"/>
@@ -1942,7 +2094,7 @@
       <c r="C32" s="7"/>
     </row>
     <row r="33" spans="29:29">
-      <c r="AC33" s="3"/>
+      <c r="AC33" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2032,7 +2184,7 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="3"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
@@ -2052,16 +2204,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="3"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -2109,7 +2261,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="5"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -2182,7 +2334,6 @@
       <c r="B6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="1"/>
       <c r="W6" s="1" t="s">
         <v>98</v>
       </c>
@@ -2196,7 +2347,6 @@
       <c r="B10" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="1"/>
       <c r="W10" s="1" t="s">
         <v>101</v>
       </c>
@@ -2208,7 +2358,7 @@
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="3"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13" spans="2:23">
       <c r="C13" s="2"/>
@@ -2217,7 +2367,6 @@
       <c r="B14" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="1"/>
       <c r="W14" s="1" t="s">
         <v>104</v>
       </c>
@@ -2226,17 +2375,16 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="5"/>
-      <c r="V16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="1"/>
       <c r="W18" s="1" t="s">
         <v>107</v>
       </c>
@@ -2260,7 +2408,291 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:AC25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:26">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:26">
+      <c r="B3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="2:26">
+      <c r="C4" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26">
+      <c r="B6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26">
+      <c r="C7" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26">
+      <c r="B9" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26">
+      <c r="C10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26">
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="2:26">
+      <c r="B12" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="V12" s="5"/>
+    </row>
+    <row r="13" spans="2:26">
+      <c r="C13" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26">
+      <c r="Z14" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26">
+      <c r="B15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="Z15" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26">
+      <c r="C16" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="V16" s="5"/>
+    </row>
+    <row r="17" spans="2:29">
+      <c r="Z17" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="2:29">
+      <c r="B18" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29">
+      <c r="C19" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="2:29">
+      <c r="Z20" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29">
+      <c r="B21" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29">
+      <c r="C22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29">
+      <c r="AC23" s="5"/>
+    </row>
+    <row r="24" spans="2:29">
+      <c r="B24" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="2:29">
+      <c r="C25" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:AC25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="B3" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="C4" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22">
+      <c r="B6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22">
+      <c r="C7" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="C13" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="B15" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="V15" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="C16" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="V16" s="5"/>
+    </row>
+    <row r="18" spans="2:29">
+      <c r="B18" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29">
+      <c r="C19" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29">
+      <c r="B21" t="s">
+        <v>156</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29">
+      <c r="C22" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29">
+      <c r="AC23" s="5"/>
+    </row>
+    <row r="24" spans="2:29">
+      <c r="B24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z24"/>
+    </row>
+    <row r="25" spans="2:29">
+      <c r="C25" s="1" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="5"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="20260308" sheetId="76" r:id="rId4"/>
     <sheet name="20260315" sheetId="77" r:id="rId5"/>
     <sheet name="20260322" sheetId="78" r:id="rId6"/>
+    <sheet name="20260426" sheetId="79" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="183">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -518,6 +519,69 @@
   </si>
   <si>
     <t>B: Tóngyì! AI ràng shēnghuó gèng gāoxiào.</t>
+  </si>
+  <si>
+    <t>A: 嘿，这个周末你想去春游吗？</t>
+  </si>
+  <si>
+    <t>A: Hey, do you want to go for a spring outing this weekend?</t>
+  </si>
+  <si>
+    <t>Hēi, zhège zhōumò nǐ xiǎng qù chūnyóu ma?</t>
+  </si>
+  <si>
+    <t>B: 听起来很棒！我们应该去哪里？</t>
+  </si>
+  <si>
+    <t>B: That sounds great! Where should we go?</t>
+  </si>
+  <si>
+    <t>Tīng qǐlái hěn bàng! Wǒmen yīnggāi qù nǎlǐ?</t>
+  </si>
+  <si>
+    <t>A: 城市公园怎么样？我听说樱花开了。</t>
+  </si>
+  <si>
+    <t>A: How about the city park? I heard the cherry blossoms are blooming.</t>
+  </si>
+  <si>
+    <t>Chéngshì gōngyuán zěnme yàng? Wǒ tīngshuō yīnghuā kāi le.</t>
+  </si>
+  <si>
+    <t>B: 太好了！我会带些零食。</t>
+  </si>
+  <si>
+    <t>B: Perfect! I'll bring some snacks.</t>
+  </si>
+  <si>
+    <t>Tài hǎo le! Wǒ huì dài xiē língshí.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A: 太棒了！我们10点见面。 </t>
+  </si>
+  <si>
+    <t>A: Awesome! Let's meet at 10 AM.</t>
+  </si>
+  <si>
+    <t>Tài bàng le! Wǒmen shí diǎn jiànmiàn.</t>
+  </si>
+  <si>
+    <t>B: 我需要带野餐垫吗？</t>
+  </si>
+  <si>
+    <t>B: Should I bring a picnic blanket too?</t>
+  </si>
+  <si>
+    <t>Wǒ xūyào dài yěcān diàn ma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A: 好主意！也许再带个飞盘玩游戏。 </t>
+  </si>
+  <si>
+    <t>A: Good idea! And maybe a frisbee for games.</t>
+  </si>
+  <si>
+    <t>Hǎo zhǔyì! Yěxǔ zài dài gè fēipán wán yóuxì.</t>
   </si>
 </sst>
 </file>
@@ -2699,4 +2763,118 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:R22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:18">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18">
+      <c r="B3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18">
+      <c r="C4" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18">
+      <c r="B6" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18">
+      <c r="C7" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18">
+      <c r="B9" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18">
+      <c r="C10" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18">
+      <c r="B12" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18">
+      <c r="C13" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18">
+      <c r="B15" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18">
+      <c r="C16" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
+      <c r="B18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
+      <c r="C19" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
+      <c r="B21" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
+      <c r="C22" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="6"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="20260315" sheetId="77" r:id="rId5"/>
     <sheet name="20260322" sheetId="78" r:id="rId6"/>
     <sheet name="20260426" sheetId="79" r:id="rId7"/>
+    <sheet name="20260510" sheetId="80" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="208">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -582,6 +583,81 @@
   </si>
   <si>
     <t>Hǎo zhǔyì! Yěxǔ zài dài gè fēipán wán yóuxì.</t>
+  </si>
+  <si>
+    <t>A: 嘿，你今天下午想去骑自行车吗？</t>
+  </si>
+  <si>
+    <t>A: Hey, do you want to go cycling this afternoon?</t>
+  </si>
+  <si>
+    <t>Hēi, nǐ jīn tiān xià wǔ xiǎng qù qí zì xíng chē ma?</t>
+  </si>
+  <si>
+    <t>B: 当然，我很想去。我们去哪里？</t>
+  </si>
+  <si>
+    <t>B: Sure, I'd love to. Where should we go?</t>
+  </si>
+  <si>
+    <t>Dāng rán, wǒ hěn xiǎng qù. Wǒ men qù nǎ lǐ?</t>
+  </si>
+  <si>
+    <t>A: 河边的小路怎么样？那里平坦而且风景好。</t>
+  </si>
+  <si>
+    <t>A: How about the riverside trail? It's flat and scenic.</t>
+  </si>
+  <si>
+    <t>Hé biān de xiǎo lù zěn me yàng? Nà lǐ píng tǎn ér qiě fēng jǐng hǎo.</t>
+  </si>
+  <si>
+    <t>B: 好主意。我会带上我的头盔和水壶。</t>
+  </si>
+  <si>
+    <t>B: Great idea. I'll bring my helmet and water bottle.</t>
+  </si>
+  <si>
+    <t>Hǎo zhǔ yì. Wǒ huì dài shàng wǒ de tóu kuī hé shuǐ hú.</t>
+  </si>
+  <si>
+    <t>人</t>
+  </si>
+  <si>
+    <t>A: 我也是。我们下午三点在公园入口见吧。</t>
+  </si>
+  <si>
+    <t>A: Me too. Let's meet at the park entrance at 3 pm.</t>
+  </si>
+  <si>
+    <t>Wǒ yě shì. Wǒ men xià wǔ sān diǎn zài gōng yuán rù kǒu jiàn ba.</t>
+  </si>
+  <si>
+    <t>B: 好的。你觉得我们需要带修理工具吗？</t>
+  </si>
+  <si>
+    <t>B: Okay. Do you think we need to bring a repair kit?</t>
+  </si>
+  <si>
+    <t>Hǎo de. Nǐ jué de wǒ men xū yào dài xiū lǐ gōng jù ma?</t>
+  </si>
+  <si>
+    <t>A: 是的，万一轮胎漏气呢。</t>
+  </si>
+  <si>
+    <t>A: Yes, just in case of a flat tire.</t>
+  </si>
+  <si>
+    <t>Shì de, wàn yī lún tāi lòu qì ne.</t>
+  </si>
+  <si>
+    <t>B: 说得对。我会装一个。</t>
+  </si>
+  <si>
+    <t>B: Good point. I'll pack one.</t>
+  </si>
+  <si>
+    <t>Shuō de duì. Wǒ huì zhuāng yí gè.</t>
   </si>
 </sst>
 </file>
@@ -2877,4 +2953,136 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:T23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:20">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20">
+      <c r="B3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20">
+      <c r="C4" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20">
+      <c r="B5" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20">
+      <c r="C6" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20">
+      <c r="B7" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20">
+      <c r="C8" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20">
+      <c r="B10" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20">
+      <c r="C11" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20">
+      <c r="M12" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20">
+      <c r="B13" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20">
+      <c r="C14" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20">
+      <c r="B16" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20">
+      <c r="C17" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20">
+      <c r="B19" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20">
+      <c r="C20" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20">
+      <c r="B22" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20">
+      <c r="C23" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="7"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet name="20260322" sheetId="78" r:id="rId6"/>
     <sheet name="20260426" sheetId="79" r:id="rId7"/>
     <sheet name="20260510" sheetId="80" r:id="rId8"/>
+    <sheet name="20260517" sheetId="81" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="235">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -658,6 +659,87 @@
   </si>
   <si>
     <t>Shuō de duì. Wǒ huì zhuāng yí gè.</t>
+  </si>
+  <si>
+    <t>A: 今天太热了！我感觉自己要融化了。</t>
+  </si>
+  <si>
+    <t>A: It's so hot today! I feel like I'm melting.</t>
+  </si>
+  <si>
+    <t>A: Jīntiān tài rè le! Wǒ gǎnjué zìjǐ yào rónghuà le.</t>
+  </si>
+  <si>
+    <t>B: 可不是嘛。我们去买冰淇淋吧。</t>
+  </si>
+  <si>
+    <t>B: Tell me about it. Let's go get some ice cream.</t>
+  </si>
+  <si>
+    <t>B: Kě bùshì ma. Wǒmen qù mǎi bīngqílín ba.</t>
+  </si>
+  <si>
+    <t>A: 好主意！你想要什么口味？</t>
+  </si>
+  <si>
+    <t>A: Great idea! What flavor do you want?</t>
+  </si>
+  <si>
+    <t>A: Hǎo zhǔyì! Nǐ xiǎng yào shénme kǒuwèi?</t>
+  </si>
+  <si>
+    <t>B: 我要芒果味的，吃起来像夏天。</t>
+  </si>
+  <si>
+    <t>B: I'll have mango. It tastes like summer.</t>
+  </si>
+  <si>
+    <t>B: Wǒ yào mángguǒ wèi de, chī qǐlái xiàng xiàtiān.</t>
+  </si>
+  <si>
+    <t>A: 我选椰子味。对了，你去过海边了吗</t>
+  </si>
+  <si>
+    <t>A: I'll go with coconut. By the way, have you been to the beach yet?</t>
+  </si>
+  <si>
+    <t>A: Wǒ xuǎn yēzi wèi. Duì le, nǐ qùguò hǎibiān le ma?</t>
+  </si>
+  <si>
+    <t>B: 还没呢。我计划这个周末去。</t>
+  </si>
+  <si>
+    <t>B: Not yet. I'm planning to go this weekend.</t>
+  </si>
+  <si>
+    <t>B: Hái méi ne. Wǒ jìhuà zhège zhōumò qù.</t>
+  </si>
+  <si>
+    <t>A: 我也是！海水一定很清凉。</t>
+  </si>
+  <si>
+    <t>A: Me too! The water must be so refreshing.</t>
+  </si>
+  <si>
+    <t>A: Wǒ yě shì! Hǎishuǐ yīdìng hěn qīngliáng.</t>
+  </si>
+  <si>
+    <t>B: 等不及要感受海风了。</t>
+  </si>
+  <si>
+    <t>B: I can't wait to feel the sea breeze.</t>
+  </si>
+  <si>
+    <t>: Děng bùjí yào gǎnshòu hǎifēng le.</t>
+  </si>
+  <si>
+    <t>A: 还可以看日落。夏天的傍晚最棒了。</t>
+  </si>
+  <si>
+    <t>A: And watch the sunset. Summer evenings are the best.</t>
+  </si>
+  <si>
+    <t>A: Hái kěyǐ kàn rìluò. Xiàtiān de bàngwǎn zuì bàng le.</t>
   </si>
 </sst>
 </file>
@@ -670,7 +752,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -681,6 +763,12 @@
       <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1170,19 +1258,16 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1191,127 +1276,131 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1940,7 +2029,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -1969,7 +2058,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="6"/>
+      <c r="C11" s="7"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -1988,7 +2077,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1997,16 +2086,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="5"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2023,19 +2112,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="4"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="5"/>
+      <c r="V22" s="6"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -2077,7 +2166,7 @@
       </c>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="7"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" spans="2:29">
       <c r="B33" s="1" t="s">
@@ -2086,7 +2175,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="5"/>
+      <c r="AC33" s="6"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -2130,7 +2219,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -2159,7 +2248,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="6"/>
+      <c r="C11" s="7"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -2178,7 +2267,7 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="U15" s="1" t="s">
         <v>47</v>
       </c>
@@ -2187,16 +2276,16 @@
       <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="5"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="U18" s="1" t="s">
         <v>50</v>
       </c>
@@ -2213,28 +2302,28 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="4"/>
       <c r="U21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="5"/>
+      <c r="V22" s="6"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="30" spans="2:26">
       <c r="B30"/>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="7"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" spans="29:29">
-      <c r="AC33" s="5"/>
+      <c r="AC33" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2315,7 +2404,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -2324,13 +2413,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="5"/>
+      <c r="V12" s="6"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -2344,16 +2433,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="4"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -2401,7 +2490,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="5"/>
+      <c r="AC23" s="6"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -2495,13 +2584,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="5"/>
+      <c r="V12" s="6"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -2515,11 +2604,11 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="4"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="4"/>
-      <c r="V16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -2548,7 +2637,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="5"/>
+      <c r="AC23" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2613,16 +2702,16 @@
       </c>
     </row>
     <row r="11" spans="2:26">
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:26">
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="V12" s="5"/>
+      <c r="V12" s="6"/>
     </row>
     <row r="13" spans="2:26">
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2635,16 +2724,16 @@
       <c r="B15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="4"/>
       <c r="Z15" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" spans="2:26">
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="17" spans="2:29">
       <c r="Z17" s="1" t="s">
@@ -2683,7 +2772,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="5"/>
+      <c r="AC23" s="6"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -2761,7 +2850,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -2772,7 +2861,7 @@
       </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2780,16 +2869,16 @@
       <c r="B15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="4"/>
       <c r="V15" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -2818,7 +2907,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="5"/>
+      <c r="AC23" s="6"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -3085,4 +3174,144 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:S28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19">
+      <c r="B3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19">
+      <c r="C4" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:19">
+      <c r="B6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19">
+      <c r="C7" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19">
+      <c r="B9" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
+      <c r="C10" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19">
+      <c r="B12" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19">
+      <c r="C13" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19">
+      <c r="B15" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
+      <c r="C16" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19">
+      <c r="B18" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19">
+      <c r="C19" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19">
+      <c r="B21" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19">
+      <c r="C22" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19">
+      <c r="B24" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19">
+      <c r="C25" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19">
+      <c r="B27" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19">
+      <c r="C28" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="8"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <sheet name="20260426" sheetId="79" r:id="rId7"/>
     <sheet name="20260510" sheetId="80" r:id="rId8"/>
     <sheet name="20260517" sheetId="81" r:id="rId9"/>
+    <sheet name="20260524" sheetId="82" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="259">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -740,6 +741,150 @@
   </si>
   <si>
     <t>A: Hái kěyǐ kàn rìluò. Xiàtiān de bàngwǎn zuì bàng le.</t>
+  </si>
+  <si>
+    <t>A: 外面正在倾盆大雨呢！我今天早上没看天气预报。</t>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>: It's pouring outside! I didn't check the weather this morning.</t>
+    </r>
+  </si>
+  <si>
+    <t>Wài miàn zhèng zài qīng pén dà yǔ ne! Wǒ jīn tiān zǎo shàng méi kàn tiān qì yù bào.</t>
+  </si>
+  <si>
+    <t>B: 我也没看！我本来打算午饭后去图书馆学习的。</t>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>: Me neither! I planned to go to the library to study after lunch.</t>
+    </r>
+  </si>
+  <si>
+    <t>Wǒ yě méi kàn! Wǒ běn lái dǎ suàn wǔ fàn hòu qù tú shū guǎn xué xí de</t>
+  </si>
+  <si>
+    <t>A: 你有多余的雨伞借给我吗？我得回宿舍取笔记本。</t>
+  </si>
+  <si>
+    <t>A:  Do you have an extra umbrella I can borrow? I need to go back to my dorm to get my notebook.</t>
+  </si>
+  <si>
+    <t>Nǐ yǒu duō yú de yǔ sǎn jiè gěi wǒ ma? Wǒ děi huí sù shè qǔ bǐ jì běn.</t>
+  </si>
+  <si>
+    <t>B: 当然有啊！我的包里总是放着一把折叠伞，就是为了雨天准备的。</t>
+  </si>
+  <si>
+    <t>B:Of course! I keep a folding umbrella in my bag all the time for rainy days.</t>
+  </si>
+  <si>
+    <t>dāng rán yǒu a! Wǒ de bāo lǐ zǒng shì fàng zhe yī bǎ zhé dié sǎn, jiù shì wèi le yǔ tiān zhǔn bèi de.</t>
+  </si>
+  <si>
+    <t>A: 真是个好习惯。今天下午这场雨下得太突然了</t>
+  </si>
+  <si>
+    <t>A: That's such a good habit. The rain came out of nowhere this afternoon.</t>
+  </si>
+  <si>
+    <t>zhēn shì gè hǎo xí guàn. Jīn tiān xià wǔ zhè cháng yǔ xià de tài tū rán le.</t>
+  </si>
+  <si>
+    <t>B: 其实我很喜欢雨后的味道，很清新，特别舒服。</t>
+  </si>
+  <si>
+    <t>B: I actually like the smell after rain—it smells fresh and clean.</t>
+  </si>
+  <si>
+    <t>qí shí wǒ hěn xǐ huan yǔ hòu de wèi dào,  hen qīng  xīn , tè bié shū fu.</t>
+  </si>
+  <si>
+    <t>A: 是啊，我也这么觉得！但是在大雨里走路总是把鞋弄得全湿。</t>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>: Yeah, I agree! But walking in the heavy rain always gets my shoes all wet</t>
+    </r>
+  </si>
+  <si>
+    <t>shì a, wǒ yě zhè me jué de! dàn shì zài dà yǔ lǐ zǒu lù zǒng shì bǎ xié nòng de quán shī.</t>
+  </si>
+  <si>
+    <t>B: 这是真的</t>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>: That's true</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">zhè shì zhēn de. </t>
   </si>
 </sst>
 </file>
@@ -752,7 +897,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -953,6 +1098,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2189,6 +2339,139 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:V26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="B3" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="C4" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:22">
+      <c r="B6" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="V6" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22">
+      <c r="C7" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="V13" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22">
+      <c r="C14" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="B15" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="C16" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="C19" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="V22" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="C23" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="V25" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="C26" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="9"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="20260510" sheetId="80" r:id="rId8"/>
     <sheet name="20260517" sheetId="81" r:id="rId9"/>
     <sheet name="20260524" sheetId="82" r:id="rId10"/>
+    <sheet name="20260531" sheetId="83" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="283">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -747,6 +748,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>A</t>
     </r>
     <r>
@@ -774,6 +780,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>B</t>
     </r>
     <r>
@@ -837,6 +848,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>A</t>
     </r>
     <r>
@@ -864,6 +880,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t>B</t>
     </r>
     <r>
@@ -885,6 +906,88 @@
   </si>
   <si>
     <t xml:space="preserve">zhè shì zhēn de. </t>
+  </si>
+  <si>
+    <t>A:  东西都收拾完啦，搬家真累呀。</t>
+  </si>
+  <si>
+    <t>A: All packed already. Moving is so tiring!</t>
+  </si>
+  <si>
+    <t>Dōng xi dōu shōu shi wán la, bān jiā zhēn lèi ya.</t>
+  </si>
+  <si>
+    <t>B: 没错，我才打包一半</t>
+  </si>
+  <si>
+    <t>B: Yep. I only finished half the packing,</t>
+  </si>
+  <si>
+    <t>méicuò, wǒ cái dǎbāo yíbàn</t>
+  </si>
+  <si>
+    <t>A: 那幅你喜欢的画，包好了吗？</t>
+  </si>
+  <si>
+    <t>A: Did you pack that painting you love?</t>
+  </si>
+  <si>
+    <t>nà fú nǐ xǐhuan de huà, bāohǎo le ma?</t>
+  </si>
+  <si>
+    <t>B: 放心，包好了。</t>
+  </si>
+  <si>
+    <t>B: Don’t worry, it’s secured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fàngxīn,  bāohǎo le </t>
+  </si>
+  <si>
+    <t>A: 新家物业说下午两点开门，赶得上吗？</t>
+  </si>
+  <si>
+    <t>A: The new place’s management will unlock the door at 2. Can we make it?</t>
+  </si>
+  <si>
+    <t>xīnjiā wùyè shuō xiàwǔ liǎng diǎn kāimén, gǎndeshàng ma?</t>
+  </si>
+  <si>
+    <t>B: 司机已经在楼下等，现在走肯定赶得上。</t>
+  </si>
+  <si>
+    <t>B: The driver’s waiting downstairs. Leaving now, we’ll definitely make it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> sījī yǐjīng zài lóuxià děng, xiànzài zǒu kěndìng gǎndeshàng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A:旧房子水电燃气都关了吗？ </t>
+  </si>
+  <si>
+    <t>A: Did you turn off water, power and gas at the old place?</t>
+  </si>
+  <si>
+    <r>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> jiùfángzi shuǐdiàn ránqì dōu guān le ma?</t>
+    </r>
+  </si>
+  <si>
+    <t>B: 都查过了，没问题。</t>
+  </si>
+  <si>
+    <t>B: Checked everything,  All good.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dōu cháguò le, méiwèntí.</t>
   </si>
 </sst>
 </file>
@@ -914,6 +1017,11 @@
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1098,11 +1206,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1408,19 +1511,16 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1429,119 +1529,122 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1549,8 +1652,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2179,7 +2283,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="3"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -2208,7 +2312,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="7"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -2227,7 +2331,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="4"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2236,16 +2340,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="6"/>
+      <c r="V16" s="7"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="6"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="4"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2262,19 +2366,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="6"/>
+      <c r="V22" s="7"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="3"/>
+      <c r="B23" s="4"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -2316,7 +2420,7 @@
       </c>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="8"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="2:29">
       <c r="B33" s="1" t="s">
@@ -2325,7 +2429,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="6"/>
+      <c r="AC33" s="7"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -2455,7 +2559,6 @@
       <c r="B25" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C25" s="1"/>
       <c r="V25" s="1" t="s">
         <v>257</v>
       </c>
@@ -2463,6 +2566,134 @@
     <row r="26" spans="2:22">
       <c r="C26" s="1" t="s">
         <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:X25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:24">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24">
+      <c r="B3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24">
+      <c r="C4" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:24">
+      <c r="B6" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="X6" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24">
+      <c r="C7" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24">
+      <c r="B9" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24">
+      <c r="C10" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24">
+      <c r="B12" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24">
+      <c r="C13" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24">
+      <c r="B15" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24">
+      <c r="C16" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24">
+      <c r="B18" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24">
+      <c r="C19" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24">
+      <c r="B21" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24">
+      <c r="C22" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24">
+      <c r="B24" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="2:24">
+      <c r="C25" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -2502,7 +2733,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="3"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -2531,7 +2762,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="7"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -2550,7 +2781,7 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="4"/>
       <c r="U15" s="1" t="s">
         <v>47</v>
       </c>
@@ -2559,16 +2790,16 @@
       <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="6"/>
+      <c r="V16" s="7"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="6"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="4"/>
       <c r="U18" s="1" t="s">
         <v>50</v>
       </c>
@@ -2585,28 +2816,28 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="U21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="6"/>
+      <c r="V22" s="7"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="3"/>
+      <c r="B23" s="4"/>
     </row>
     <row r="30" spans="2:26">
       <c r="B30"/>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="8"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="29:29">
-      <c r="AC33" s="6"/>
+      <c r="AC33" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2687,7 +2918,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="4"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -2696,13 +2927,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="6"/>
+      <c r="V12" s="7"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="4"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -2716,16 +2947,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="6"/>
+      <c r="V16" s="7"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -2773,7 +3004,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="6"/>
+      <c r="AC23" s="7"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -2867,13 +3098,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="6"/>
+      <c r="V12" s="7"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="3"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -2887,11 +3118,11 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="5"/>
-      <c r="V16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="V16" s="7"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -2920,7 +3151,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="6"/>
+      <c r="AC23" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2985,16 +3216,16 @@
       </c>
     </row>
     <row r="11" spans="2:26">
-      <c r="C11" s="3"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" spans="2:26">
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="V12" s="6"/>
+      <c r="V12" s="7"/>
     </row>
     <row r="13" spans="2:26">
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3007,16 +3238,16 @@
       <c r="B15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="Z15" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" spans="2:26">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="V16" s="6"/>
+      <c r="V16" s="7"/>
     </row>
     <row r="17" spans="2:29">
       <c r="Z17" s="1" t="s">
@@ -3055,7 +3286,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="6"/>
+      <c r="AC23" s="7"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -3133,7 +3364,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="3"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -3144,7 +3375,7 @@
       </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3152,16 +3383,16 @@
       <c r="B15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="V15" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="V16" s="6"/>
+      <c r="V16" s="7"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -3190,7 +3421,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="6"/>
+      <c r="AC23" s="7"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" activeTab="10"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="1" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="20260517" sheetId="81" r:id="rId9"/>
     <sheet name="20260524" sheetId="82" r:id="rId10"/>
     <sheet name="20260531" sheetId="83" r:id="rId11"/>
+    <sheet name="20260614" sheetId="84" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="310">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -969,6 +970,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>‌</t>
     </r>
     <r>
@@ -988,6 +994,87 @@
   </si>
   <si>
     <t xml:space="preserve"> dōu cháguò le, méiwèntí.</t>
+  </si>
+  <si>
+    <t>A: 这周末公司组织团建，大家都去吗？</t>
+  </si>
+  <si>
+    <t>A: This weekend the company is organizing a team-building event. Is everyone going?</t>
+  </si>
+  <si>
+    <t>Zhè zhōumò gōngsī zǔzhī tuánjiàn, dàjiā dōu qù ma?</t>
+  </si>
+  <si>
+    <t>B: 当然去啊，听说这次是去山里露营。</t>
+  </si>
+  <si>
+    <t>B: Of course! I heard we’re going camping in the mountains this time.</t>
+  </si>
+  <si>
+    <t>Dāngrán qù a, tīngshuō zhè cì shì qù shān lǐ lùyíng.</t>
+  </si>
+  <si>
+    <t>A: 真的吗？终于可以放松一下了。</t>
+  </si>
+  <si>
+    <t>A: Really? Finally, we can relax a bit.</t>
+  </si>
+  <si>
+    <t>Zhēn de ma? Zhōngyú kěyǐ fàngsōng yīxià le</t>
+  </si>
+  <si>
+    <t>B:  我们要自己带帐篷吗？我还没有呢。</t>
+  </si>
+  <si>
+    <t>B:Do we need to bring our own tents? I don’t have one yet.</t>
+  </si>
+  <si>
+    <t>Wǒmen yào zìjǐ dài zhàngpeng ma? Wǒ hái méiyǒu ne</t>
+  </si>
+  <si>
+    <t>A:好像公司统一租了，不用担心。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> It seems the company has rented them all together, so no worries.</t>
+  </si>
+  <si>
+    <t>Hǎoxiàng gōngsī tǒngyī zū le, bùyòng dāoxīn.</t>
+  </si>
+  <si>
+    <t>B:  那我们需要带什么？零食可以带吧。</t>
+  </si>
+  <si>
+    <t>So what do we need to bring? We can bring snacks, right?</t>
+  </si>
+  <si>
+    <t>Nà wǒmen xūyào dài shénme? Língshí kěyǐ dài ba.</t>
+  </si>
+  <si>
+    <t>A: 我已经买了薯片和饮料！</t>
+  </si>
+  <si>
+    <t>A:  I’ve already bought chips and drinks!</t>
+  </si>
+  <si>
+    <t>Wǒ yǐjīng mǎi le shǔpiàn hé yǐnliào!</t>
+  </si>
+  <si>
+    <t>B: 听说晚上还安排了篝火晚会。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I heard there’s also a bonfire party planned for the evening.</t>
+  </si>
+  <si>
+    <t>Tīngshuō wǎnshang hái ānpái le gōuhuǒ wǎnhuì.</t>
+  </si>
+  <si>
+    <t>A:太好了！可以唱歌聊天</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A: Awesome! We can sing and chat. </t>
+  </si>
+  <si>
+    <t>Tài hǎo le! Kěyǐ chànggē liáotiān</t>
   </si>
 </sst>
 </file>
@@ -2703,6 +2790,150 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:V27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="2:22">
+      <c r="C2" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="C3" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="C5" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:22">
+      <c r="C6" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="S6" s="2"/>
+    </row>
+    <row r="8" spans="2:22">
+      <c r="C8" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="C9" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="C11" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="C12" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22">
+      <c r="C14" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="C15" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="17" spans="3:22">
+      <c r="C17" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22">
+      <c r="C18" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="3:22">
+      <c r="C20" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22">
+      <c r="C21" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22">
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="3:22">
+      <c r="C23" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22">
+      <c r="C24" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22">
+      <c r="C26" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22">
+      <c r="C27" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="1" activeTab="11"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="2" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="20260524" sheetId="82" r:id="rId10"/>
     <sheet name="20260531" sheetId="83" r:id="rId11"/>
     <sheet name="20260614" sheetId="84" r:id="rId12"/>
+    <sheet name="20260621" sheetId="85" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="338">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1075,6 +1076,90 @@
   </si>
   <si>
     <t>Tài hǎo le! Kěyǐ chànggē liáotiān</t>
+  </si>
+  <si>
+    <t>A: 嘿，我在考虑自己组装一台电脑。有什么建议吗？</t>
+  </si>
+  <si>
+    <t>A: Hey, I'm thinking about building my own PC. Any tips?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A: Hēi, wǒ zài kǎolǜ zìjǐ zǔzhuāng yī tái diànnǎo. </t>
+  </si>
+  <si>
+    <t>Yǒu shénme jiànyì ma?</t>
+  </si>
+  <si>
+    <t>B: 太棒了！首先，确定你的预算和用途。</t>
+  </si>
+  <si>
+    <t>B: Awesome! First, decide your budget and what you'll use it for.</t>
+  </si>
+  <si>
+    <t>B: Tài bàngle! Shǒuxiān, quèdìng nǐ de yùsuàn hé yòngtú.</t>
+  </si>
+  <si>
+    <t>A: 主要是玩游戏。预算大概1200美元。</t>
+  </si>
+  <si>
+    <t>A: Mostly gaming. Around $1,200.</t>
+  </si>
+  <si>
+    <t>A: Zhǔyào shì wán yóuxì, Yùsuàn dàgài 1200 měiyuán.</t>
+  </si>
+  <si>
+    <t>B: 很好。先从CPU和显卡开始——它们是主机的核心。</t>
+  </si>
+  <si>
+    <t>B: Great. Start with the CPU and GPU — they're the heart of your build.</t>
+  </si>
+  <si>
+    <t>B: Hěn hǎo. Xiān cóng CPU hé xiǎnkǎ kāishǐ——tāmen shì zhǔjī de héxīn.</t>
+  </si>
+  <si>
+    <t>A: 我看中了AMD Ryzen 5和RTX 3060。</t>
+  </si>
+  <si>
+    <t>A: I'm eyeing an AMD Ryzen 5 and an RTX 3060.</t>
+  </si>
+  <si>
+    <t>A: Wǒ kànzhòngle AMD Ryzen 5 hé RTX 3060.</t>
+  </si>
+  <si>
+    <t>B: 不错的选择。确保主板和CPU兼容。</t>
+  </si>
+  <si>
+    <t>B: Solid choices. Make sure your motherboard is compatible with the CPU.</t>
+  </si>
+  <si>
+    <t>B: Bùcuò de xuǎnzé. Quèbǎo zhǔbǎn hé CPU jiānróng.</t>
+  </si>
+  <si>
+    <t>A: 明白了。内存和硬盘方面呢？</t>
+  </si>
+  <si>
+    <t>A: Got it. What about memory and storage?</t>
+  </si>
+  <si>
+    <t>A: Míngbáile. Nèicún hé yìngpán fāngmiàn ne?</t>
+  </si>
+  <si>
+    <t>B: 16GB内存是黄金选择。再配个固态硬盘，开机速度飞快。</t>
+  </si>
+  <si>
+    <t>B: 16GB RAM is the sweet spot. Get an SSD for fast boot times.</t>
+  </si>
+  <si>
+    <t>B: 16GB nèicún shì huángjīn xuǎnzé. Zài pèi gè gùtài yìngpán, kāijī sùdù fēikuài.</t>
+  </si>
+  <si>
+    <t>A: 谢谢！我这周末就开始挑选零件。</t>
+  </si>
+  <si>
+    <t>A: Thanks! I'll start picking parts this weekend.</t>
+  </si>
+  <si>
+    <t>A: Xièxiè! Wǒ zhè zhōumò jiù kāishǐ tiāoxuǎn língjiàn.</t>
   </si>
 </sst>
 </file>
@@ -2934,6 +3019,161 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:X28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:24">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24">
+      <c r="B3" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="X3" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24">
+      <c r="C4" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24">
+      <c r="C5" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:24">
+      <c r="B6" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="S6" s="2"/>
+      <c r="X6" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24">
+      <c r="C7" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24">
+      <c r="B9" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="X9" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24">
+      <c r="C10" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24">
+      <c r="B12" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="X12" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24">
+      <c r="C13" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24">
+      <c r="B15" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="X15" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24">
+      <c r="C16" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24">
+      <c r="B18" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="X18" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24">
+      <c r="C19" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24">
+      <c r="B21" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="X21" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24">
+      <c r="C22" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24">
+      <c r="B24" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="X24" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="25" spans="2:24">
+      <c r="C25" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24">
+      <c r="B27" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="X27" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24">
+      <c r="C28" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="2" activeTab="12"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="3" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="20260531" sheetId="83" r:id="rId11"/>
     <sheet name="20260614" sheetId="84" r:id="rId12"/>
     <sheet name="20260621" sheetId="85" r:id="rId13"/>
+    <sheet name="20260627" sheetId="86" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="363">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1160,6 +1161,81 @@
   </si>
   <si>
     <t>A: Xièxiè! Wǒ zhè zhōumò jiù kāishǐ tiāoxuǎn língjiàn.</t>
+  </si>
+  <si>
+    <t>A: 嘿智能音箱，请打开客厅的灯。</t>
+  </si>
+  <si>
+    <t>A: Hey smart speaker, turn on the living room lamp please.</t>
+  </si>
+  <si>
+    <t>Hēi zhì néng yīn xiāng, qǐng dǎ kāi kè tīng de dēng.</t>
+  </si>
+  <si>
+    <t>B:好的，客厅的主灯已经打开了。</t>
+  </si>
+  <si>
+    <t>B: Sure, the living room main light has been switched on.</t>
+  </si>
+  <si>
+    <t>Hǎo de, kè tīng de zhǔ dēng yǐ jīng dǎ kāi le.</t>
+  </si>
+  <si>
+    <t>A: 你可以把空调调到24摄氏度吗？</t>
+  </si>
+  <si>
+    <t>A: Can you adjust the air conditioner to 24 degrees Celsius?</t>
+  </si>
+  <si>
+    <t>Nǐ kě yǐ bǎ kōngtiáo   tiáo dào èr shí sì shè shì dù ma?</t>
+  </si>
+  <si>
+    <t>B: 操作完成，空调温度现在是24度。</t>
+  </si>
+  <si>
+    <t>B: Completed, the AC temperature is now 24℃.</t>
+  </si>
+  <si>
+    <t>Cāo zuò wán chéng, kōng tiáo wēn dù xiàn zài shì èr shí dù.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A:我还想在卧室音箱上播放轻柔的音乐。 </t>
+  </si>
+  <si>
+    <t>A:  I also want to play soft music on the bedroom speaker.</t>
+  </si>
+  <si>
+    <t>Wǒ hái xiǎng zài wòshì yīnxiāng shàng bōfàng qīngróu de yīn yuè.</t>
+  </si>
+  <si>
+    <t>B: 正在立即播放你最喜欢的睡前歌单。</t>
+  </si>
+  <si>
+    <t>B: Playing your favorite bedtime playlist right now.</t>
+  </si>
+  <si>
+    <t>Zhèngzài lìjí bōfàng nǐ zuì xǐhuān de shuìqián gēdān.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A:只用声音控制所有设备真是太方便了。 </t>
+  </si>
+  <si>
+    <t>A:  It’s so convenient to control all devices with just voice.</t>
+  </si>
+  <si>
+    <t>Zhǐyòng shēngyīn kòngzhì suǒyǒu shèbèi zhēn shì tài fāngbiàn le.</t>
+  </si>
+  <si>
+    <t>B: 是的，这种智能家居生活感觉真的很棒</t>
+  </si>
+  <si>
+    <t>B: Yeah, this smart home life feels really nice.</t>
+  </si>
+  <si>
+    <t>Shì de, zhè zhǒng zhìnéng jiājū shēnghuó gǎn jué zhēn de hěn bàng.</t>
+  </si>
+  <si>
+    <t>居住</t>
   </si>
 </sst>
 </file>
@@ -3039,7 +3115,6 @@
       <c r="B3" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C3" s="1"/>
       <c r="X3" s="1" t="s">
         <v>311</v>
       </c>
@@ -3058,7 +3133,6 @@
       <c r="B6" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C6" s="1"/>
       <c r="S6" s="2"/>
       <c r="X6" s="1" t="s">
         <v>315</v>
@@ -3073,7 +3147,6 @@
       <c r="B9" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C9" s="1"/>
       <c r="X9" s="1" t="s">
         <v>318</v>
       </c>
@@ -3087,7 +3160,6 @@
       <c r="B12" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C12" s="1"/>
       <c r="X12" s="1" t="s">
         <v>321</v>
       </c>
@@ -3101,7 +3173,6 @@
       <c r="B15" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C15" s="1"/>
       <c r="X15" s="1" t="s">
         <v>324</v>
       </c>
@@ -3115,7 +3186,6 @@
       <c r="B18" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C18" s="1"/>
       <c r="X18" s="1" t="s">
         <v>327</v>
       </c>
@@ -3129,7 +3199,6 @@
       <c r="B21" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C21" s="1"/>
       <c r="X21" s="1" t="s">
         <v>330</v>
       </c>
@@ -3143,7 +3212,6 @@
       <c r="B24" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C24" s="1"/>
       <c r="X24" s="1" t="s">
         <v>333</v>
       </c>
@@ -3157,7 +3225,6 @@
       <c r="B27" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C27" s="1"/>
       <c r="X27" s="1" t="s">
         <v>336</v>
       </c>
@@ -3165,6 +3232,143 @@
     <row r="28" spans="2:24">
       <c r="C28" s="1" t="s">
         <v>337</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:V27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="B3" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="C4" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:22">
+      <c r="B6" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="V6" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22">
+      <c r="C7" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="C13" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="B15" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="V15" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="C16" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="V18" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="C19" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="V21" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="C22" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="V24" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="C25" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="L27" s="1" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="3" activeTab="13"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="4" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="20260614" sheetId="84" r:id="rId12"/>
     <sheet name="20260621" sheetId="85" r:id="rId13"/>
     <sheet name="20260627" sheetId="86" r:id="rId14"/>
+    <sheet name="20260705" sheetId="88" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="364">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1237,6 +1238,9 @@
   <si>
     <t>居住</t>
   </si>
+  <si>
+    <t>Duì, gōng chǎng lǐ de jī qì rén huì zǔzhuāng chǎn pǐn。</t>
+  </si>
 </sst>
 </file>
 
@@ -1261,20 +1265,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="等线"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Times New Roman"/>
+      <color rgb="FFCE181E"/>
+      <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1289,9 +1288,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFCE181E"/>
-      <name val="等线"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2531,7 +2535,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="4"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -2579,7 +2583,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="2"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2588,16 +2592,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="7"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="7"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="2"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2614,19 +2618,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="4"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="7"/>
+      <c r="V22" s="3"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="4"/>
+      <c r="B23" s="2"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -2677,7 +2681,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="7"/>
+      <c r="AC33" s="3"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -2724,7 +2728,7 @@
       <c r="B6" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
       <c r="V6" s="1" t="s">
         <v>239</v>
       </c>
@@ -2856,7 +2860,7 @@
       <c r="B6" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
       <c r="X6" s="1" t="s">
         <v>263</v>
       </c>
@@ -2927,7 +2931,7 @@
       </c>
     </row>
     <row r="22" spans="2:24">
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="7" t="s">
         <v>279</v>
       </c>
     </row>
@@ -2992,7 +2996,7 @@
       <c r="C6" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
     </row>
     <row r="8" spans="2:22">
       <c r="C8" s="1" t="s">
@@ -3060,7 +3064,7 @@
       </c>
     </row>
     <row r="22" spans="3:22">
-      <c r="C22" s="3"/>
+      <c r="C22" s="7"/>
     </row>
     <row r="23" spans="3:22">
       <c r="C23" s="1" t="s">
@@ -3133,7 +3137,7 @@
       <c r="B6" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
       <c r="X6" s="1" t="s">
         <v>315</v>
       </c>
@@ -3204,7 +3208,7 @@
       </c>
     </row>
     <row r="22" spans="2:24">
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="7" t="s">
         <v>331</v>
       </c>
     </row>
@@ -3274,7 +3278,7 @@
       <c r="B6" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
       <c r="V6" s="1" t="s">
         <v>342</v>
       </c>
@@ -3314,7 +3318,6 @@
       <c r="B15" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C15" s="1"/>
       <c r="V15" s="1" t="s">
         <v>351</v>
       </c>
@@ -3328,7 +3331,6 @@
       <c r="B18" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C18" s="1"/>
       <c r="V18" s="1" t="s">
         <v>354</v>
       </c>
@@ -3342,7 +3344,7 @@
       <c r="B21" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="7"/>
       <c r="V21" s="1" t="s">
         <v>357</v>
       </c>
@@ -3356,7 +3358,6 @@
       <c r="B24" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C24" s="1"/>
       <c r="V24" s="1" t="s">
         <v>360</v>
       </c>
@@ -3369,6 +3370,204 @@
     <row r="27" spans="2:22">
       <c r="L27" s="1" t="s">
         <v>362</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:AC28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="B3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="C4" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="B5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22">
+      <c r="C6" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22">
+      <c r="B7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22">
+      <c r="C8" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="B11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="P11" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="C12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="V12" s="3"/>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="B13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="P13" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22">
+      <c r="C14" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="B15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="P15" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="C16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="2:29">
+      <c r="B17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="2:29">
+      <c r="C18" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29">
+      <c r="B19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="2:29">
+      <c r="C20" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29">
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29">
+      <c r="C22" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29">
+      <c r="B23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC23" s="3"/>
+    </row>
+    <row r="24" spans="2:29">
+      <c r="C24" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="2:29">
+      <c r="B25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="2:29">
+      <c r="C26" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="2:29">
+      <c r="B27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="2:29">
+      <c r="C28" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3408,7 +3607,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="4"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -3456,7 +3655,7 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="2"/>
       <c r="U15" s="1" t="s">
         <v>47</v>
       </c>
@@ -3465,16 +3664,16 @@
       <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="7"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="7"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="2"/>
       <c r="U18" s="1" t="s">
         <v>50</v>
       </c>
@@ -3491,19 +3690,19 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="4"/>
       <c r="U21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="7"/>
+      <c r="V22" s="3"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="4"/>
+      <c r="B23" s="2"/>
     </row>
     <row r="30" spans="2:26">
       <c r="B30"/>
@@ -3512,7 +3711,7 @@
       <c r="C32" s="9"/>
     </row>
     <row r="33" spans="29:29">
-      <c r="AC33" s="7"/>
+      <c r="AC33" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -3593,7 +3792,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="2"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -3602,13 +3801,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="7"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="2"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -3622,16 +3821,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="4"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="7"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -3679,7 +3878,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="7"/>
+      <c r="AC23" s="3"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -3773,13 +3972,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="7"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="4"/>
+      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -3793,11 +3992,11 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="4"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="6"/>
-      <c r="V16" s="7"/>
+      <c r="C16" s="5"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -3826,7 +4025,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="7"/>
+      <c r="AC23" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -3891,16 +4090,16 @@
       </c>
     </row>
     <row r="11" spans="2:26">
-      <c r="C11" s="4"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:26">
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="V12" s="7"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13" spans="2:26">
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3913,16 +4112,16 @@
       <c r="B15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="4"/>
       <c r="Z15" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" spans="2:26">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="V16" s="7"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:29">
       <c r="Z17" s="1" t="s">
@@ -3961,7 +4160,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="7"/>
+      <c r="AC23" s="3"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -4039,7 +4238,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="4"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4050,7 +4249,7 @@
       </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>149</v>
       </c>
     </row>
@@ -4058,16 +4257,16 @@
       <c r="B15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="4"/>
       <c r="V15" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="V16" s="7"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -4096,7 +4295,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="7"/>
+      <c r="AC23" s="3"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -4398,7 +4597,7 @@
       <c r="B6" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="S6" s="6" t="s">
         <v>212</v>
       </c>
     </row>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="4" activeTab="14"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="5" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="20260621" sheetId="85" r:id="rId13"/>
     <sheet name="20260627" sheetId="86" r:id="rId14"/>
     <sheet name="20260705" sheetId="88" r:id="rId15"/>
+    <sheet name="20260719" sheetId="89" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="395">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1240,6 +1241,99 @@
   </si>
   <si>
     <t>Duì, gōng chǎng lǐ de jī qì rén huì zǔzhuāng chǎn pǐn。</t>
+  </si>
+  <si>
+    <t>A: 今天的台风真大。</t>
+  </si>
+  <si>
+    <t>A: The typhoon is really strong today.</t>
+  </si>
+  <si>
+    <t>A: Jīntiān de táifēng zhēn dà.</t>
+  </si>
+  <si>
+    <t>B: 是啊，外面风在呼啸。</t>
+  </si>
+  <si>
+    <t>B: Yeah, the wind is howling outside.</t>
+  </si>
+  <si>
+    <t>B: Shì a, wàimiàn fēng zài hūxiào.</t>
+  </si>
+  <si>
+    <t>A: 你听到雨打在窗户上的声音了吗？</t>
+  </si>
+  <si>
+    <t>A: Did you hear the rain pounding on the windows?</t>
+  </si>
+  <si>
+    <t>A: Nǐ tīngdào yǔ dǎ zài chuānghù shàng de shēngyīn le ma?</t>
+  </si>
+  <si>
+    <t>B: 从大清早就一直这样了。</t>
+  </si>
+  <si>
+    <t>B: It's been like this since early morning.</t>
+  </si>
+  <si>
+    <t>B: Cóng dàqīngzǎo jiù yīzhí zhèyàng le.</t>
+  </si>
+  <si>
+    <t>A: 我看到一些树被风吹弯了</t>
+  </si>
+  <si>
+    <t>A: I saw some trees bending low in the wind.</t>
+  </si>
+  <si>
+    <t>A: Wǒ kàndào yīxiē shù bèi fēng chuī wān le</t>
+  </si>
+  <si>
+    <t>B: 天气预报说会持续一整天。</t>
+  </si>
+  <si>
+    <t>B: The weather forecast says it will last all day.</t>
+  </si>
+  <si>
+    <t>B: Tiānqì yùbào shuō huì chíxù yī zhěng tiān.</t>
+  </si>
+  <si>
+    <t>keep</t>
+  </si>
+  <si>
+    <t>A: 我们应该待在室内，不要出门。</t>
+  </si>
+  <si>
+    <t>A: We should stay indoors and not go out.</t>
+  </si>
+  <si>
+    <t>A: Wǒmen yīnggāi dāi zài shìnèi, bùyào chūmén.</t>
+  </si>
+  <si>
+    <t>B: 好主意。我已经准备了一些食物和水。</t>
+  </si>
+  <si>
+    <t>B: Good idea. I've already prepared some food and water.</t>
+  </si>
+  <si>
+    <t>B: Hǎo zhǔyì. Wǒ yǐjīng zhǔnbèi le yīxiē shíwù hé shuǐ.</t>
+  </si>
+  <si>
+    <t>A: 希望不要停电。</t>
+  </si>
+  <si>
+    <t>A: Let's hope the power doesn't go out.</t>
+  </si>
+  <si>
+    <t>A: Xīwàng bùyào tíngdiàn.</t>
+  </si>
+  <si>
+    <t>B: 我已经准备好手电筒，以防万一。</t>
+  </si>
+  <si>
+    <t>B: I have a flashlight ready just in case.</t>
+  </si>
+  <si>
+    <t>B: Wǒ yǐjīng zhǔnbèi hǎo shǒudiàntǒng, yǐfáng wànyī.</t>
   </si>
 </sst>
 </file>
@@ -1266,14 +1360,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFCE181E"/>
       <name val="等线"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFCE181E"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2535,7 +2629,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -2583,7 +2677,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2592,16 +2686,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="2"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="3"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2627,10 +2721,10 @@
       <c r="C22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="3"/>
+      <c r="V22" s="2"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -2681,7 +2775,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="3"/>
+      <c r="AC33" s="2"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -3451,7 +3545,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -3460,13 +3554,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="3"/>
+      <c r="V12" s="2"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -3489,7 +3583,7 @@
       <c r="C16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="2"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -3537,7 +3631,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="2"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -3568,6 +3662,171 @@
     <row r="28" spans="2:29">
       <c r="C28" s="1" t="s">
         <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:V23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="B3" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="C4" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="B5" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="S5" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22">
+      <c r="C6" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22">
+      <c r="B7" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22">
+      <c r="C8" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="S9" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="B11" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="S11" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="12" ht="14" customHeight="1" spans="2:22">
+      <c r="C12" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="V12" s="2"/>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="B13" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="S13" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22">
+      <c r="C14" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="K15" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="B16" t="s">
+        <v>383</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19">
+      <c r="C17" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19">
+      <c r="B18" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="S18" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19">
+      <c r="C19" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19">
+      <c r="B20" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19">
+      <c r="C21" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19">
+      <c r="B22" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19">
+      <c r="C23" s="1" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -3607,7 +3866,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -3655,7 +3914,7 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="U15" s="1" t="s">
         <v>47</v>
       </c>
@@ -3664,16 +3923,16 @@
       <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="2"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="3"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="U18" s="1" t="s">
         <v>50</v>
       </c>
@@ -3699,10 +3958,10 @@
       <c r="C22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="3"/>
+      <c r="V22" s="2"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="30" spans="2:26">
       <c r="B30"/>
@@ -3711,7 +3970,7 @@
       <c r="C32" s="9"/>
     </row>
     <row r="33" spans="29:29">
-      <c r="AC33" s="3"/>
+      <c r="AC33" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -3792,7 +4051,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -3801,13 +4060,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="3"/>
+      <c r="V12" s="2"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -3830,7 +4089,7 @@
       <c r="C16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="2"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -3878,7 +4137,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="2"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -3972,13 +4231,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="3"/>
+      <c r="V12" s="2"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -3996,7 +4255,7 @@
     </row>
     <row r="16" spans="2:23">
       <c r="C16" s="5"/>
-      <c r="V16" s="3"/>
+      <c r="V16" s="2"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -4025,7 +4284,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4090,16 +4349,16 @@
       </c>
     </row>
     <row r="11" spans="2:26">
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:26">
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="V12" s="3"/>
+      <c r="V12" s="2"/>
     </row>
     <row r="13" spans="2:26">
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>122</v>
       </c>
     </row>
@@ -4121,7 +4380,7 @@
       <c r="C16" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="2"/>
     </row>
     <row r="17" spans="2:29">
       <c r="Z17" s="1" t="s">
@@ -4160,7 +4419,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="2"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -4238,7 +4497,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4249,7 +4508,7 @@
       </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>149</v>
       </c>
     </row>
@@ -4266,7 +4525,7 @@
       <c r="C16" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="2"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -4295,7 +4554,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="2"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="5" activeTab="15"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="6" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="20260627" sheetId="86" r:id="rId14"/>
     <sheet name="20260705" sheetId="88" r:id="rId15"/>
     <sheet name="20260719" sheetId="89" r:id="rId16"/>
+    <sheet name="20260726" sheetId="90" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="426">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1334,6 +1335,99 @@
   </si>
   <si>
     <t>B: Wǒ yǐjīng zhǔnbèi hǎo shǒudiàntǒng, yǐfáng wànyī.</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>A: 你一般怎么消暑？</t>
+  </si>
+  <si>
+    <t>A: What do you usually do to beat the heat?</t>
+  </si>
+  <si>
+    <t>Nǐ yībān zěnme xiāoshǔ?</t>
+  </si>
+  <si>
+    <t>B: 我吃很多西瓜，然后待在屋里吹空调。</t>
+  </si>
+  <si>
+    <t>B: I eat lots of watermelon and stay indoors with the AC on.</t>
+  </si>
+  <si>
+    <t>B: Wǒ chī hěn duō xīguā, ránhòu dāi zài wū lǐ chuī kōngtiáo.</t>
+  </si>
+  <si>
+    <t>A: 我也是。我还喜欢周末去海边。</t>
+  </si>
+  <si>
+    <t>A: Same here. I also love going to the beach on weekends.</t>
+  </si>
+  <si>
+    <t>Wǒ yě shì. Wǒ hái xǐhuān zhōumò qù hǎibiān.</t>
+  </si>
+  <si>
+    <t>B: 听起来不错。你会在海里游泳吗？</t>
+  </si>
+  <si>
+    <t>B: That sounds fun. Do you swim in the ocean?</t>
+  </si>
+  <si>
+    <t>Tīng qǐlái búcuò. Nǐ huì zài hǎi lǐ yóuyǒng ma?</t>
+  </si>
+  <si>
+    <t>A: 会的，但只在早上人不多的时候去。</t>
+  </si>
+  <si>
+    <t>A: Yes, but only in the morning when it's not too crowded.</t>
+  </si>
+  <si>
+    <t>Huì de, dàn zhǐ zài zǎoshang rén bù duō de shíhòu qù.</t>
+  </si>
+  <si>
+    <t>B: 聪明。我更喜欢傍晚太阳下山后去散步。</t>
+  </si>
+  <si>
+    <t>B: Smart. I prefer evening walks when the sun goes down.</t>
+  </si>
+  <si>
+    <t>Cōngmíng. Wǒ gèng xǐhuān bàngwǎn tàiyáng xiàshān hòu qù sànbù.</t>
+  </si>
+  <si>
+    <t>A: 那时候的微风感觉特别舒服，对吧？</t>
+  </si>
+  <si>
+    <t>A: The breeze feels amazing at that time, doesn't it?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nà shíhòu de wēifēng gǎnjué tèbié shūfú, duì ba?</t>
+  </si>
+  <si>
+    <t>B: 没错。而且日落美极了。</t>
+  </si>
+  <si>
+    <t>B: Absolutely. And the sunsets are gorgeous.</t>
+  </si>
+  <si>
+    <t>Méicuò. Érqiě rìluò měi jí le.</t>
+  </si>
+  <si>
+    <t>A: 我们哪天傍晚一起去散步吧。</t>
+  </si>
+  <si>
+    <t>A: We should go for a walk together one evening.</t>
+  </si>
+  <si>
+    <t>Wǒmen nǎ tiān bàngwǎn yīqǐ qù sànbù ba.</t>
+  </si>
+  <si>
+    <t>B: 好主意。就这周五吧！</t>
+  </si>
+  <si>
+    <t>B: Great idea. Let's do it this Friday!</t>
+  </si>
+  <si>
+    <t>Hǎo zhǔyì. Jiù zhè zhōuwǔ ba!</t>
   </si>
 </sst>
 </file>
@@ -3704,7 +3798,6 @@
       <c r="B5" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C5" s="1"/>
       <c r="S5" s="1" t="s">
         <v>368</v>
       </c>
@@ -3731,7 +3824,6 @@
       <c r="B9" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C9" s="1"/>
       <c r="S9" s="1" t="s">
         <v>374</v>
       </c>
@@ -3761,7 +3853,6 @@
       <c r="B13" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C13" s="1"/>
       <c r="S13" s="1" t="s">
         <v>380</v>
       </c>
@@ -3793,7 +3884,6 @@
       <c r="B18" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C18" s="1"/>
       <c r="S18" s="1" t="s">
         <v>387</v>
       </c>
@@ -3827,6 +3917,172 @@
     <row r="23" spans="2:19">
       <c r="C23" s="1" t="s">
         <v>394</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:V31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="2:22">
+      <c r="C2" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="B3" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="C4" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22">
+      <c r="B6" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22">
+      <c r="B7" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22">
+      <c r="V8" s="2"/>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="V9" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1" spans="2:22">
+      <c r="C11" s="5"/>
+      <c r="V11" s="2"/>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="C13" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="B15" t="s">
+        <v>408</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="C16" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="C19" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="C22" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="C25" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="B27" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="C28" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22">
+      <c r="B30" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22">
+      <c r="C31" s="1" t="s">
+        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="6" activeTab="16"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="8" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="20260705" sheetId="88" r:id="rId15"/>
     <sheet name="20260719" sheetId="89" r:id="rId16"/>
     <sheet name="20260726" sheetId="90" r:id="rId17"/>
+    <sheet name="20260802" sheetId="92" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="426">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1454,14 +1455,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="等线"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFCE181E"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1476,6 +1477,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
@@ -1484,12 +1491,6 @@
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2088,12 +2089,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2723,7 +2724,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="3"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -2752,7 +2753,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="8"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -2771,7 +2772,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="2"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2780,16 +2781,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="2"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="2"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="2"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2806,19 +2807,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="2"/>
+      <c r="V22" s="4"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="3"/>
+      <c r="B23" s="2"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -2860,7 +2861,7 @@
       </c>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="9"/>
+      <c r="C32" s="7"/>
     </row>
     <row r="33" spans="2:29">
       <c r="B33" s="1" t="s">
@@ -2869,7 +2870,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="2"/>
+      <c r="AC33" s="4"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -2916,7 +2917,7 @@
       <c r="B6" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="S6" s="6"/>
+      <c r="S6" s="8"/>
       <c r="V6" s="1" t="s">
         <v>239</v>
       </c>
@@ -3048,7 +3049,7 @@
       <c r="B6" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="S6" s="6"/>
+      <c r="S6" s="8"/>
       <c r="X6" s="1" t="s">
         <v>263</v>
       </c>
@@ -3119,7 +3120,7 @@
       </c>
     </row>
     <row r="22" spans="2:24">
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="9" t="s">
         <v>279</v>
       </c>
     </row>
@@ -3184,7 +3185,7 @@
       <c r="C6" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="S6" s="6"/>
+      <c r="S6" s="8"/>
     </row>
     <row r="8" spans="2:22">
       <c r="C8" s="1" t="s">
@@ -3252,7 +3253,7 @@
       </c>
     </row>
     <row r="22" spans="3:22">
-      <c r="C22" s="7"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" spans="3:22">
       <c r="C23" s="1" t="s">
@@ -3325,7 +3326,7 @@
       <c r="B6" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="S6" s="6"/>
+      <c r="S6" s="8"/>
       <c r="X6" s="1" t="s">
         <v>315</v>
       </c>
@@ -3396,7 +3397,7 @@
       </c>
     </row>
     <row r="22" spans="2:24">
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="9" t="s">
         <v>331</v>
       </c>
     </row>
@@ -3466,7 +3467,7 @@
       <c r="B6" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="S6" s="6"/>
+      <c r="S6" s="8"/>
       <c r="V6" s="1" t="s">
         <v>342</v>
       </c>
@@ -3532,7 +3533,7 @@
       <c r="B21" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C21" s="7"/>
+      <c r="C21" s="9"/>
       <c r="V21" s="1" t="s">
         <v>357</v>
       </c>
@@ -3639,7 +3640,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -3648,13 +3649,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="2"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="2"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -3668,16 +3669,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="2"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -3725,7 +3726,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="2"/>
+      <c r="AC23" s="4"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -3827,10 +3828,10 @@
       <c r="S9" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="V9" s="2"/>
+      <c r="V9" s="4"/>
     </row>
     <row r="10" spans="2:22">
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>375</v>
       </c>
     </row>
@@ -3838,16 +3839,16 @@
       <c r="B11" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="5"/>
       <c r="S11" s="1" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1" spans="2:22">
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="V12" s="2"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
@@ -3974,25 +3975,25 @@
       </c>
     </row>
     <row r="8" spans="2:22">
-      <c r="V8" s="2"/>
+      <c r="V8" s="4"/>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="2"/>
       <c r="V9" s="1" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="10" spans="2:22">
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1" spans="2:22">
-      <c r="C11" s="5"/>
-      <c r="V11" s="2"/>
+      <c r="C11" s="6"/>
+      <c r="V11" s="4"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4083,6 +4084,196 @@
     <row r="31" spans="2:22">
       <c r="C31" s="1" t="s">
         <v>425</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:AC34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="2:22">
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22">
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="V15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V16" s="4"/>
+    </row>
+    <row r="17" spans="2:26">
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="2:26">
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="V18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26">
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26">
+      <c r="Z20"/>
+    </row>
+    <row r="21" spans="2:26">
+      <c r="B21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="V21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26">
+      <c r="C22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="V22" s="4"/>
+    </row>
+    <row r="23" spans="2:26">
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="2:26">
+      <c r="B24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26">
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26">
+      <c r="B27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26">
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26">
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="2:26">
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26">
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" spans="2:29">
+      <c r="B33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC33" s="4"/>
+    </row>
+    <row r="34" spans="2:29">
+      <c r="C34" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4122,7 +4313,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="3"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -4151,7 +4342,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="8"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4170,7 +4361,7 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="2"/>
       <c r="U15" s="1" t="s">
         <v>47</v>
       </c>
@@ -4179,16 +4370,16 @@
       <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="2"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="2"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="2"/>
       <c r="U18" s="1" t="s">
         <v>50</v>
       </c>
@@ -4205,28 +4396,28 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="U21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="2"/>
+      <c r="V22" s="4"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="3"/>
+      <c r="B23" s="2"/>
     </row>
     <row r="30" spans="2:26">
       <c r="B30"/>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="9"/>
+      <c r="C32" s="7"/>
     </row>
     <row r="33" spans="29:29">
-      <c r="AC33" s="2"/>
+      <c r="AC33" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4307,7 +4498,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -4316,13 +4507,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="2"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="2"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -4336,16 +4527,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="2"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -4393,7 +4584,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="2"/>
+      <c r="AC23" s="4"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -4487,13 +4678,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="2"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="3"/>
+      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -4507,11 +4698,11 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="5"/>
-      <c r="V16" s="2"/>
+      <c r="C16" s="6"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -4540,7 +4731,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="2"/>
+      <c r="AC23" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4605,16 +4796,16 @@
       </c>
     </row>
     <row r="11" spans="2:26">
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:26">
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="V12" s="2"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:26">
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -4627,16 +4818,16 @@
       <c r="B15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="Z15" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" spans="2:26">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="V16" s="2"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:29">
       <c r="Z17" s="1" t="s">
@@ -4675,7 +4866,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="2"/>
+      <c r="AC23" s="4"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -4753,7 +4944,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4764,7 +4955,7 @@
       </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>149</v>
       </c>
     </row>
@@ -4772,16 +4963,16 @@
       <c r="B15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="V15" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="V16" s="2"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -4810,7 +5001,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="2"/>
+      <c r="AC23" s="4"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -5112,7 +5303,7 @@
       <c r="B6" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="S6" s="8" t="s">
         <v>212</v>
       </c>
     </row>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="8" activeTab="17"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="8" activeTab="18"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="20260719" sheetId="89" r:id="rId16"/>
     <sheet name="20260726" sheetId="90" r:id="rId17"/>
     <sheet name="20260802" sheetId="92" r:id="rId18"/>
+    <sheet name="20260809" sheetId="93" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="426">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1452,6 +1453,12 @@
       <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1481,12 +1488,6 @@
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2089,8 +2090,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2724,7 +2725,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -2753,7 +2754,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="3"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -2772,7 +2773,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2781,16 +2782,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="4"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2807,19 +2808,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="6"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="4"/>
+      <c r="V22" s="5"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -2861,7 +2862,7 @@
       </c>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="7"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" spans="2:29">
       <c r="B33" s="1" t="s">
@@ -2870,7 +2871,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="4"/>
+      <c r="AC33" s="5"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -2917,7 +2918,7 @@
       <c r="B6" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="S6" s="8"/>
+      <c r="S6" s="2"/>
       <c r="V6" s="1" t="s">
         <v>239</v>
       </c>
@@ -3049,7 +3050,7 @@
       <c r="B6" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="S6" s="8"/>
+      <c r="S6" s="2"/>
       <c r="X6" s="1" t="s">
         <v>263</v>
       </c>
@@ -3185,7 +3186,7 @@
       <c r="C6" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="S6" s="8"/>
+      <c r="S6" s="2"/>
     </row>
     <row r="8" spans="2:22">
       <c r="C8" s="1" t="s">
@@ -3326,7 +3327,7 @@
       <c r="B6" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="S6" s="8"/>
+      <c r="S6" s="2"/>
       <c r="X6" s="1" t="s">
         <v>315</v>
       </c>
@@ -3467,7 +3468,7 @@
       <c r="B6" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="S6" s="8"/>
+      <c r="S6" s="2"/>
       <c r="V6" s="1" t="s">
         <v>342</v>
       </c>
@@ -3640,7 +3641,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -3649,13 +3650,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="4"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -3669,16 +3670,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="6"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -3726,7 +3727,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="5"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -3828,10 +3829,10 @@
       <c r="S9" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="V9" s="4"/>
+      <c r="V9" s="5"/>
     </row>
     <row r="10" spans="2:22">
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>375</v>
       </c>
     </row>
@@ -3839,16 +3840,16 @@
       <c r="B11" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="C11" s="6"/>
       <c r="S11" s="1" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1" spans="2:22">
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="V12" s="4"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
@@ -3975,25 +3976,25 @@
       </c>
     </row>
     <row r="8" spans="2:22">
-      <c r="V8" s="4"/>
+      <c r="V8" s="5"/>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="3"/>
       <c r="V9" s="1" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="10" spans="2:22">
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1" spans="2:22">
-      <c r="C11" s="6"/>
-      <c r="V11" s="4"/>
+      <c r="C11" s="7"/>
+      <c r="V11" s="5"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4123,7 +4124,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -4152,7 +4153,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="3"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4171,7 +4172,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -4180,16 +4181,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="4"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -4206,19 +4207,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="6"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="4"/>
+      <c r="V22" s="5"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -4260,7 +4261,7 @@
       </c>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="7"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" spans="2:29">
       <c r="B33" s="1" t="s">
@@ -4269,11 +4270,143 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="4"/>
+      <c r="AC33" s="5"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
         <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:V25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="B3" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="C4" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:22">
+      <c r="B6" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="V6" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22">
+      <c r="C7" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="V13" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22">
+      <c r="C14" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="B15" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="C16" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="C19" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="V22" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="C23" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="C25" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -4313,7 +4446,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -4342,7 +4475,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="3"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4361,7 +4494,7 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="U15" s="1" t="s">
         <v>47</v>
       </c>
@@ -4370,16 +4503,16 @@
       <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="4"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="U18" s="1" t="s">
         <v>50</v>
       </c>
@@ -4396,28 +4529,28 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="6"/>
       <c r="U21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="4"/>
+      <c r="V22" s="5"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="30" spans="2:26">
       <c r="B30"/>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="7"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" spans="29:29">
-      <c r="AC33" s="4"/>
+      <c r="AC33" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4498,7 +4631,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -4507,13 +4640,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="4"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -4527,16 +4660,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="6"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -4584,7 +4717,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="5"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -4678,13 +4811,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="4"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -4698,11 +4831,11 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="6"/>
-      <c r="V16" s="4"/>
+      <c r="C16" s="7"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -4731,7 +4864,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4796,16 +4929,16 @@
       </c>
     </row>
     <row r="11" spans="2:26">
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:26">
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="V12" s="4"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13" spans="2:26">
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>122</v>
       </c>
     </row>
@@ -4818,16 +4951,16 @@
       <c r="B15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="6"/>
       <c r="Z15" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" spans="2:26">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:29">
       <c r="Z17" s="1" t="s">
@@ -4866,7 +4999,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="5"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -4944,7 +5077,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4955,7 +5088,7 @@
       </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>149</v>
       </c>
     </row>
@@ -4963,16 +5096,16 @@
       <c r="B15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="6"/>
       <c r="V15" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -5001,7 +5134,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="5"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -5303,7 +5436,7 @@
       <c r="B6" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="S6" s="2" t="s">
         <v>212</v>
       </c>
     </row>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Chinese_lessons\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="8" activeTab="18"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="9" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -26,6 +31,7 @@
     <sheet name="20260726" sheetId="90" r:id="rId17"/>
     <sheet name="20260802" sheetId="92" r:id="rId18"/>
     <sheet name="20260809" sheetId="93" r:id="rId19"/>
+    <sheet name="20260816" sheetId="94" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="456">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1431,6 +1437,134 @@
   <si>
     <t>Hǎo zhǔyì. Jiù zhè zhōuwǔ ba!</t>
   </si>
+  <si>
+    <t>A: 你平时用AI写代码吗？</t>
+  </si>
+  <si>
+    <t>A:Do you usually use AI to write code?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nǐ píngshí yòng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> xiě dàimǎ ma?</t>
+    </r>
+  </si>
+  <si>
+    <t>B: 用啊，写个脚本什么的很快。</t>
+  </si>
+  <si>
+    <t>B: Yeah, it's fast for writing scripts and some.</t>
+  </si>
+  <si>
+    <t>Yòng a, xiě gè jiǎoběn shénme de hěn kuài</t>
+  </si>
+  <si>
+    <t>A: 不怕它写出bug来？</t>
+  </si>
+  <si>
+    <t>A: Aren't you afraid it'll introduce bugs?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bù pà tā xiě chū </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>bug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> lái?</t>
+    </r>
+  </si>
+  <si>
+    <t>B: 怕，所以每次都得自己再过一遍</t>
+  </si>
+  <si>
+    <t>B: I am, so I always review everything myself.</t>
+  </si>
+  <si>
+    <t>Pà, suǒyǐ měi cì dōu dei zìjǐ zài guò yībiàn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A:我感觉它更适合当个辅助 </t>
+  </si>
+  <si>
+    <t>A: I feel like it's better as an assistant</t>
+  </si>
+  <si>
+    <t>Wǒ gǎnjué tā gèng shìhé dāng gè fǔzhù</t>
+  </si>
+  <si>
+    <t>B: 对，逻辑框架还是得自己搭</t>
+  </si>
+  <si>
+    <t>B: Right, you still have to build the logic yourself</t>
+  </si>
+  <si>
+    <t>Duì, luójí kuàngjià háishì dei zìjǐ dā</t>
+  </si>
+  <si>
+    <t>A: 完全交给它还是不放心</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A:  I wouldn't trust it with everything. </t>
+  </si>
+  <si>
+    <t>wánquán jiāo gěi tā háishì bù fàngxīn.</t>
+  </si>
+  <si>
+    <t>B:  毕竟它不懂业务上下文嘛</t>
+  </si>
+  <si>
+    <t>B: After all, it doesn't understand the business context</t>
+  </si>
+  <si>
+    <t>Bìjìng tā bù dǒng yèwù shàngxiàwén ma</t>
+  </si>
+  <si>
+    <t>A: 说到底，工具是好工具。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A:At the end of the day, it's a good tool </t>
+  </si>
+  <si>
+    <t>Shuō dàodǐ, gōngjù shì hǎo gōngjù</t>
+  </si>
+  <si>
+    <t>B: 关键看用的人怎么用。</t>
+  </si>
+  <si>
+    <t>B: It all depends on how you use it</t>
+  </si>
+  <si>
+    <t>Guānjiàn kàn yòng de rén zěnme yòng.</t>
+  </si>
 </sst>
 </file>
 
@@ -1442,7 +1576,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1648,6 +1782,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -4559,6 +4699,160 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:S31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19">
+      <c r="B3" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19">
+      <c r="C4" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:19">
+      <c r="B6" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="S6" s="2"/>
+    </row>
+    <row r="7" spans="2:19">
+      <c r="C7" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19">
+      <c r="B9" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
+      <c r="C10" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19">
+      <c r="B12" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19">
+      <c r="C13" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19">
+      <c r="B15" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
+      <c r="C16" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
+      <c r="B18" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
+      <c r="C19" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
+      <c r="B21" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
+      <c r="C22" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
+      <c r="B24" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
+      <c r="C25" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
+      <c r="B27" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18">
+      <c r="C28" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="B30" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
+      <c r="C31" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="9" activeTab="19"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="10" activeTab="20"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="20260802" sheetId="92" r:id="rId18"/>
     <sheet name="20260809" sheetId="93" r:id="rId19"/>
     <sheet name="20260816" sheetId="94" r:id="rId20"/>
+    <sheet name="20260823" sheetId="95" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="456">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1445,6 +1446,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Nǐ píngshí yòng </t>
     </r>
     <r>
@@ -1482,6 +1488,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Bù pà tā xiě chū </t>
     </r>
     <r>
@@ -1589,12 +1600,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="等线"/>
       <charset val="1"/>
@@ -1615,6 +1620,12 @@
       <sz val="11"/>
       <color rgb="FF1C1C1C"/>
       <name val="等线"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2231,10 +2242,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -2865,7 +2876,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="3"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -2894,7 +2905,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="4"/>
+      <c r="C11" s="7"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -2913,7 +2924,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="2"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2922,16 +2933,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="5"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="2"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2948,19 +2959,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="6"/>
+      <c r="C21" s="4"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="5"/>
+      <c r="V22" s="3"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="3"/>
+      <c r="B23" s="2"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -3011,7 +3022,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="5"/>
+      <c r="AC33" s="3"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -3058,7 +3069,7 @@
       <c r="B6" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
       <c r="V6" s="1" t="s">
         <v>239</v>
       </c>
@@ -3190,7 +3201,7 @@
       <c r="B6" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
       <c r="X6" s="1" t="s">
         <v>263</v>
       </c>
@@ -3326,7 +3337,7 @@
       <c r="C6" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
     </row>
     <row r="8" spans="2:22">
       <c r="C8" s="1" t="s">
@@ -3467,7 +3478,7 @@
       <c r="B6" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
       <c r="X6" s="1" t="s">
         <v>315</v>
       </c>
@@ -3608,7 +3619,7 @@
       <c r="B6" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
       <c r="V6" s="1" t="s">
         <v>342</v>
       </c>
@@ -3781,7 +3792,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -3790,13 +3801,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="5"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="2"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -3810,16 +3821,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="4"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -3867,7 +3878,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="5"/>
+      <c r="AC23" s="3"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -3969,10 +3980,10 @@
       <c r="S9" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="V9" s="5"/>
+      <c r="V9" s="3"/>
     </row>
     <row r="10" spans="2:22">
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>375</v>
       </c>
     </row>
@@ -3980,16 +3991,16 @@
       <c r="B11" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="4"/>
       <c r="S11" s="1" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1" spans="2:22">
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="V12" s="5"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
@@ -4116,25 +4127,25 @@
       </c>
     </row>
     <row r="8" spans="2:22">
-      <c r="V8" s="5"/>
+      <c r="V8" s="3"/>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="2"/>
       <c r="V9" s="1" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="10" spans="2:22">
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1" spans="2:22">
-      <c r="C11" s="7"/>
-      <c r="V11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="V11" s="3"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4264,7 +4275,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="3"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -4293,7 +4304,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="4"/>
+      <c r="C11" s="7"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4312,7 +4323,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="2"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -4321,16 +4332,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="5"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="2"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -4347,19 +4358,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="6"/>
+      <c r="C21" s="4"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="5"/>
+      <c r="V22" s="3"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="3"/>
+      <c r="B23" s="2"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -4410,7 +4421,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="5"/>
+      <c r="AC33" s="3"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -4457,7 +4468,7 @@
       <c r="B6" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
       <c r="V6" s="1" t="s">
         <v>239</v>
       </c>
@@ -4586,7 +4597,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="3"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -4615,7 +4626,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="4"/>
+      <c r="C11" s="7"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4634,7 +4645,7 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="2"/>
       <c r="U15" s="1" t="s">
         <v>47</v>
       </c>
@@ -4643,16 +4654,16 @@
       <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="5"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="2"/>
       <c r="U18" s="1" t="s">
         <v>50</v>
       </c>
@@ -4669,19 +4680,19 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="6"/>
+      <c r="C21" s="4"/>
       <c r="U21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="5"/>
+      <c r="V22" s="3"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="3"/>
+      <c r="B23" s="2"/>
     </row>
     <row r="30" spans="2:26">
       <c r="B30"/>
@@ -4690,7 +4701,7 @@
       <c r="C32" s="8"/>
     </row>
     <row r="33" spans="29:29">
-      <c r="AC33" s="5"/>
+      <c r="AC33" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4735,7 +4746,7 @@
       <c r="R6" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="6"/>
     </row>
     <row r="7" spans="2:19">
       <c r="C7" s="1" t="s">
@@ -4845,6 +4856,122 @@
       <c r="C31" s="1" t="s">
         <v>455</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:AC23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:23">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:23">
+      <c r="B3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="2:23">
+      <c r="B4" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23">
+      <c r="B6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23">
+      <c r="B7" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23">
+      <c r="B10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="2:23">
+      <c r="B11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="2:23">
+      <c r="V12" s="3"/>
+    </row>
+    <row r="13" spans="2:23">
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="2:23">
+      <c r="B14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="2:23">
+      <c r="B15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="2:23">
+      <c r="C16" s="5"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="18" spans="2:29">
+      <c r="B18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29">
+      <c r="B19" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29">
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29">
+      <c r="B22" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29">
+      <c r="AC23" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4925,7 +5052,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -4934,13 +5061,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="5"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="2"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -4954,16 +5081,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="4"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -5011,7 +5138,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="5"/>
+      <c r="AC23" s="3"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -5105,13 +5232,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="5"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="3"/>
+      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -5125,11 +5252,11 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="4"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="7"/>
-      <c r="V16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -5158,7 +5285,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="5"/>
+      <c r="AC23" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5223,16 +5350,16 @@
       </c>
     </row>
     <row r="11" spans="2:26">
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:26">
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="V12" s="5"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13" spans="2:26">
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5245,16 +5372,16 @@
       <c r="B15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="4"/>
       <c r="Z15" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" spans="2:26">
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:29">
       <c r="Z17" s="1" t="s">
@@ -5293,7 +5420,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="5"/>
+      <c r="AC23" s="3"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -5371,7 +5498,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -5382,7 +5509,7 @@
       </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5390,16 +5517,16 @@
       <c r="B15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="4"/>
       <c r="V15" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -5428,7 +5555,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="5"/>
+      <c r="AC23" s="3"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -5730,7 +5857,7 @@
       <c r="B6" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="S6" s="6" t="s">
         <v>212</v>
       </c>
     </row>
